--- a/review-results/复盘信息抓取-20260820.xlsx
+++ b/review-results/复盘信息抓取-20260820.xlsx
@@ -5055,8 +5055,8 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="7"/>
-    <col width="8" customWidth="1" min="8" max="9"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="8" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
@@ -5136,8 +5136,27 @@
       <c r="E2" s="3" t="n">
         <v>432.468</v>
       </c>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>790.073</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>419.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5161,8 +5180,27 @@
       <c r="E3" s="3" t="n">
         <v>434.308</v>
       </c>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>638.421</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>380.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5186,8 +5224,27 @@
       <c r="E4" s="3" t="n">
         <v>403.543</v>
       </c>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>635.636</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>389.7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5211,8 +5268,27 @@
       <c r="E5" s="3" t="n">
         <v>380.853</v>
       </c>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>634.833</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>389.7</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5236,8 +5312,27 @@
       <c r="E6" s="3" t="n">
         <v>382.508</v>
       </c>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>633.798</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>389.7</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5261,8 +5356,27 @@
       <c r="E7" s="3" t="n">
         <v>399.643</v>
       </c>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>637.095</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>392.3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5286,8 +5400,27 @@
       <c r="E8" s="3" t="n">
         <v>409.81</v>
       </c>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>786.477</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>438.49</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5311,8 +5444,27 @@
       <c r="E9" s="3" t="n">
         <v>406.77</v>
       </c>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>675.249</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>402.41</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5336,8 +5488,27 @@
       <c r="E10" s="3" t="n">
         <v>370.215</v>
       </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>462.367</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>260.06</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5361,8 +5532,27 @@
       <c r="E11" s="3" t="n">
         <v>346.688</v>
       </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>452.593</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5386,8 +5576,27 @@
       <c r="E12" s="3" t="n">
         <v>346.845</v>
       </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>452.373</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>249.05</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5411,8 +5620,27 @@
       <c r="E13" s="3" t="n">
         <v>346.773</v>
       </c>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>460.737</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>244.79</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5436,8 +5664,27 @@
       <c r="E14" s="3" t="n">
         <v>356.568</v>
       </c>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>487.016</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>343.08</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5461,8 +5708,27 @@
       <c r="E15" s="3" t="n">
         <v>361.308</v>
       </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>495.532</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>328.96</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5486,8 +5752,27 @@
       <c r="E16" s="3" t="n">
         <v>358.438</v>
       </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>593.846</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>372.09</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5511,8 +5796,27 @@
       <c r="E17" s="3" t="n">
         <v>375.143</v>
       </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>542.348</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>367.01</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5536,8 +5840,27 @@
       <c r="E18" s="3" t="n">
         <v>417.51</v>
       </c>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>798.016</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>434.99</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5561,8 +5884,27 @@
       <c r="E19" s="3" t="n">
         <v>435.49</v>
       </c>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>811.075</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>402.41</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5586,8 +5928,27 @@
       <c r="E20" s="3" t="n">
         <v>429.425</v>
       </c>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>784.006</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>411.76</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5611,8 +5972,27 @@
       <c r="E21" s="3" t="n">
         <v>426.955</v>
       </c>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>628.296</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>389.7</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5636,8 +6016,27 @@
       <c r="E22" s="3" t="n">
         <v>414.258</v>
       </c>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>631.987</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>389.7</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5661,8 +6060,27 @@
       <c r="E23" s="3" t="n">
         <v>410.883</v>
       </c>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>632.139</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>389.7</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5686,8 +6104,27 @@
       <c r="E24" s="3" t="n">
         <v>419.408</v>
       </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>633.001</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>389.7</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5711,8 +6148,27 @@
       <c r="E25" s="3" t="n">
         <v>420.835</v>
       </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>637.322</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>389.7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17809,20 +18265,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>实际系统负荷</t>
+          <t>现货日前交易价格曲线</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>新能源实际发电曲线</t>
+          <t>实际系统负荷</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -17835,7 +18291,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>日前非市场化机组总出力</t>
+          <t>新能源实际发电曲线</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -17848,7 +18304,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>省间联络线输电情况</t>
+          <t>日前非市场化机组总出力</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -17861,24 +18317,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>各时段各类电源电量</t>
+          <t>省间联络线输电情况</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>960</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>各时段各类电源的开机台数</t>
+          <t>各时段各类电源电量</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>768</v>
+        <v>960</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
@@ -17887,30 +18343,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>实时储能充电计划及电价</t>
+          <t>各时段各类电源的开机台数</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>768</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>日前储能充电计划及电价</t>
+          <t>实时储能充电计划及电价</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>96</v>
       </c>
       <c r="C10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>日前储能充电计划及电价</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="11"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/review-results/复盘信息抓取-20260820.xlsx
+++ b/review-results/复盘信息抓取-20260820.xlsx
@@ -1043,20 +1043,20 @@
   <dimension ref="A1:T97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="6" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="4" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="17" customWidth="1" min="17" max="17"/>
     <col width="10" customWidth="1" min="18" max="18"/>
@@ -5049,17 +5049,15 @@
   <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="2"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="7"/>
-    <col width="22" customWidth="1" min="8" max="9"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="8" max="9"/>
+    <col width="4" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6184,33 +6182,31 @@
   <dimension ref="A1:AB97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
     <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="26" customWidth="1" min="19" max="19"/>
-    <col width="8" customWidth="1" min="20" max="20"/>
-    <col width="8" customWidth="1" min="21" max="21"/>
-    <col width="8" customWidth="1" min="22" max="22"/>
-    <col width="12" customWidth="1" min="23" max="24"/>
-    <col width="8" customWidth="1" min="24" max="24"/>
-    <col width="8" customWidth="1" min="25" max="26"/>
-    <col width="8" customWidth="1" min="26" max="26"/>
-    <col width="8" customWidth="1" min="27" max="27"/>
-    <col width="8" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="7" customWidth="1" min="23" max="24"/>
+    <col width="5" customWidth="1" min="25" max="26"/>
+    <col width="6" customWidth="1" min="27" max="27"/>
+    <col width="7" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15576,12 +15572,11 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="6"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18227,9 +18222,9 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
